--- a/public/uploads/vouchers/Single_Voucher.xlsx
+++ b/public/uploads/vouchers/Single_Voucher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Financial_System\financial-app\public\uploads\vouchers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E05B184-0CB0-43E4-9255-3A713E897F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4DE6BC-D57B-49B9-8E4C-79B432D3B13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -515,40 +513,52 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -559,41 +569,29 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1196,12 +1194,12 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="31" t="s">
+      <c r="N4" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="33"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="40"/>
       <c r="R4" s="8"/>
       <c r="S4" s="9" t="s">
         <v>3</v>
@@ -1231,12 +1229,12 @@
       <c r="K5" s="12"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="32"/>
       <c r="R5" s="13"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
@@ -1276,10 +1274,10 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="39"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="48"/>
       <c r="R6" s="13"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
@@ -1328,12 +1326,12 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
       <c r="K8" s="2"/>
       <c r="L8" s="18" t="s">
         <v>13</v>
@@ -1355,37 +1353,37 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="18" customHeight="1">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="43" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="54" t="s">
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="56" t="s">
+      <c r="L9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="58" t="s">
+      <c r="M9" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="32"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
@@ -1394,31 +1392,31 @@
       <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="18" customHeight="1">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46" t="s">
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="59"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="45"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="34"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
@@ -1427,33 +1425,33 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="60" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="36"/>
-      <c r="M11" s="48" t="s">
+      <c r="L11" s="32"/>
+      <c r="M11" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="32"/>
-      <c r="U11" s="33"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="40"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
@@ -1492,8 +1490,8 @@
       <c r="J12" s="19">
         <v>13</v>
       </c>
-      <c r="K12" s="59"/>
-      <c r="L12" s="45"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="19">
         <v>16</v>
       </c>
@@ -1529,35 +1527,35 @@
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="24" customHeight="1">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="61" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="L13" s="36"/>
-      <c r="M13" s="34" t="s">
+      <c r="L13" s="32"/>
+      <c r="M13" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="N13" s="36"/>
-      <c r="O13" s="63">
+      <c r="N13" s="32"/>
+      <c r="O13" s="59">
         <v>13195.09</v>
       </c>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="32"/>
       <c r="V13" s="15"/>
       <c r="W13" s="15"/>
       <c r="X13" s="15"/>
@@ -1566,70 +1564,64 @@
       <c r="AA13" s="15"/>
     </row>
     <row r="14" spans="1:27" ht="24" customHeight="1">
-      <c r="A14" s="62"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="59"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="45"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="34"/>
       <c r="V14" s="15"/>
-      <c r="W14" s="20">
-        <f>1374.37/0.12</f>
-        <v>11453.083333333299</v>
-      </c>
+      <c r="W14" s="15"/>
       <c r="X14" s="15"/>
       <c r="Y14" s="15"/>
       <c r="Z14" s="15"/>
       <c r="AA14" s="15"/>
     </row>
     <row r="15" spans="1:27" ht="24" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="49" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="33"/>
-      <c r="M15" s="50" t="s">
+      <c r="L15" s="40"/>
+      <c r="M15" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="33"/>
-      <c r="O15" s="51">
+      <c r="N15" s="40"/>
+      <c r="O15" s="50">
         <v>9125.89</v>
       </c>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="33"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="40"/>
       <c r="V15" s="15"/>
-      <c r="W15" s="20">
-        <f>W14*1.12</f>
-        <v>12827.4533333333</v>
-      </c>
+      <c r="W15" s="15"/>
       <c r="X15" s="15"/>
       <c r="Y15" s="15"/>
       <c r="Z15" s="15"/>
@@ -1646,23 +1638,20 @@
       <c r="H16" s="21"/>
       <c r="I16" s="21"/>
       <c r="J16" s="21"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="33"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="40"/>
       <c r="M16" s="22"/>
       <c r="N16" s="23"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="33"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="40"/>
       <c r="V16" s="15"/>
       <c r="W16" s="15"/>
-      <c r="X16" s="15">
-        <f>12827.5-1374.37</f>
-        <v>11453.13</v>
-      </c>
+      <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
       <c r="Z16" s="15"/>
       <c r="AA16" s="15"/>
@@ -1678,24 +1667,21 @@
       <c r="H17" s="21"/>
       <c r="I17" s="21"/>
       <c r="J17" s="21"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="33"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="40"/>
       <c r="M17" s="24"/>
       <c r="N17" s="25"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="33"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="40"/>
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
       <c r="X17" s="15"/>
-      <c r="Y17" s="15">
-        <f>4308/1.12</f>
-        <v>3846.4285714285702</v>
-      </c>
+      <c r="Y17" s="15"/>
       <c r="Z17" s="15"/>
       <c r="AA17" s="15"/>
     </row>
@@ -1710,93 +1696,90 @@
       <c r="H18" s="21"/>
       <c r="I18" s="21"/>
       <c r="J18" s="21"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="33"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="40"/>
       <c r="M18" s="24"/>
       <c r="N18" s="25"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="33"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="39"/>
+      <c r="U18" s="40"/>
       <c r="V18" s="15"/>
       <c r="W18" s="15"/>
       <c r="X18" s="15"/>
-      <c r="Y18" s="15">
-        <f>Y17*0.12</f>
-        <v>461.57142857142799</v>
-      </c>
+      <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
       <c r="AA18" s="26"/>
     </row>
     <row r="19" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
       <c r="K19" s="27"/>
-      <c r="L19" s="57" t="s">
+      <c r="L19" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="M19" s="61" t="s">
+      <c r="M19" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="N19" s="36"/>
-      <c r="O19" s="64">
+      <c r="N19" s="32"/>
+      <c r="O19" s="35">
         <f>SUM(O13:U18)</f>
         <v>22320.98</v>
       </c>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
       <c r="K20" s="28"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="45"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="37"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="29"/>
     </row>
@@ -1822,10 +1805,10 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
@@ -1851,10 +1834,10 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
       <c r="Z22" s="2"/>
       <c r="AA22" s="29"/>
     </row>
@@ -1880,10 +1863,10 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
@@ -1909,13 +1892,10 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-      <c r="V24" s="30">
-        <f>O19+O43</f>
-        <v>22320.98</v>
-      </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
@@ -1941,10 +1921,10 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
     </row>
@@ -30227,6 +30207,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="M11:U11"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="M9:U10"/>
+    <mergeCell ref="M13:N14"/>
+    <mergeCell ref="O13:U14"/>
     <mergeCell ref="M19:N20"/>
     <mergeCell ref="O19:U20"/>
     <mergeCell ref="A19:J19"/>
@@ -30243,22 +30239,6 @@
     <mergeCell ref="O17:U17"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="O18:U18"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="M11:U11"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:U15"/>
-    <mergeCell ref="M9:U10"/>
-    <mergeCell ref="M13:N14"/>
-    <mergeCell ref="O13:U14"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="N5:Q5"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
